--- a/results-list/brasildefato.xlsx
+++ b/results-list/brasildefato.xlsx
@@ -35,7 +35,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-      **** pais_br jornal_brasildefato * ano_2022 
+      **** *pais_br *jornal_brasildefato *ano_2022 
       Que el gobierno de Jair Bolsonaro diera marcha atrás en su decisión de bloquear el presupuesto de las universidades fue, en cierto modo, un alivio para las instituciones. Sin embargo, una nueva decisión publicada el 6 de octubre en el Diario Oficial del país muestra que el ataque a la educación continúa: R$ 616 millones (aprox. 119 millones USD) fueron bloqueados del presupuesto del Ministerio de Ciencia, Tecnología e Innovación (MCTI) destinados a actividades de investigación en las universidades públicas.
 Los recortes afectan a decenas de proyectos esenciales para el avance científico y tecnológico de Brasil en las más diversas áreas, que quedan definitivamente cancelados.
 Por ejemplo, se cortaron R$ 30 millones (aprox. 6 millones USD) para el "Fomento de Proyectos Institucionales de Investigación en el Sector Salud". Solo el área de "Fomento de la Investigación y Desarrollo en Áreas Básicas y Estratégicas" sufrió un recorte de alrededor de R$ 177 millones (aprox. 34 millones USD).
@@ -60,7 +60,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-      **** pais_br jornal_brasildefato * ano_2023 
+      **** *pais_br *jornal_brasildefato *ano_2023 
       No se necesita veneno ni trabajo forzado para eliminar las malas hierbas. Es posible, por ejemplo, administrar más adecuadamente el agua que fluye a través de los kilómetros de tuberías que riegan las plantaciones de arroz de tipo "agulhinha" o "cateto". Tampoco son necesarios los fertilizantes químicos para aumentar la productividad de la tierra. Se pueden recuperar saberes ancestrales y organizar la producción en masa en una fábrica de bioinsumos, que no son tóxicos ni contaminantes.
 Desde hace más de dos décadas, las familias agricultoras del Movimiento de Trabajadores Rurales Sin Tierra (MST), en Brasil, insisten en la misión de producir arroz orgánico, equilibrando la generación de ingresos con el respeto al medio ambiente. Los pioneros tuvieron que desarrollar su propio método de cultivo y competir por el espacio con la agroindustria y su forma de sembrar. Y lo lograron.
 El arroz agroecológico del MST ganó protagonismo en el debate político al figurar, según el Instituto Rio Grandense del Arroz (IRGA), como la mayor producción orgánica de América Latina. Gracias al conocimiento acumulado por los propios agricultores –y con la ayuda de universidades y organismos públicos locales–, tanto el área sembrada como la producción total están creciendo, incluso ante una reducción en la producción nacional de arroz.
@@ -115,7 +115,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-      **** pais_br jornal_brasildefato * ano_2023 
+      **** *pais_br *jornal_brasildefato *ano_2023 
       Endeudados con organismos multilaterales como el Banco Mundial y el FMI, muchos países del Sur Global fomentan el modelo de producción agrícola de monocultivo para la exportación en un intento de recaudar dólares para pagar sus deudas. Este es el análisis de Morgan Ody, actual coordinadora de la Vía Campesina, la plataforma fundada en 1993 que reúne a los principales movimientos de la lucha campesina de todas las regiones del mundo.
 En entrevista con Brasil de Fato, Ody afirmó que el agronegocio profundiza la situación de dependencia externa de muchos países frente a las grandes corporaciones del sector de la producción de alimentos, pero también frente a los grandes bancos y entidades financieras.
 "El Banco Mundial, el Fondo Monetario, estos organismos multilaterales hacen que los países del Sur, pero también los pueblos del Norte, se endeuden en dólares, una moneda sobre la cual, salvo los Estados Unidos, ningún otro país tiene control. Entonces, para pagar la deuda, estos países necesitan divisas y para hacerlo terminan priorizando un modelo agroexportador, en lugar de producir alimentos para las personas", afirmó.
@@ -168,7 +168,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-      **** pais_br jornal_brasildefato * ano_2022 
+      **** *pais_br *jornal_brasildefato *ano_2022 
       Na sexta, 24, em palestra na 19ª Jornada de Agroecologia, em Curitiba, João Pedro Stédile, da direção nacional do MST, falou sobre os três modelos de produção agrícola que coexistem no Brasil há, pelo menos, 30 anos. Destacando que dois deles são ligados ao capital e, apenas, um aos trabalhadores.
 Nesse primeiro grupo elenca o latifúndio, explica que não é apenas sinônimo de grande propriedade, mas sim um modelo de expropriar a natureza, explorar seus recursos. “Eles se apropriam de forma privada de bens que deveriam ser comuns, se apropriam das terras, das águas, da biodiversidade, dos minérios etc.”, afirma Stédile. Diz ainda que com a atual crise do capitalismo muitos foram explorar esses recursos, porque dão muito lucro e rapidamente, e que por trás dos lúmpens, que desmatam, mineram, estão grandes empresas estrangeiras, que ficam com a maior parte do lucro.
 Agronegócio O outro modelo, também ligado ao capital, é o agronegócio. Que, explica, é baseado em grandes extensões de terra, no monocultivo, uso de sementes transgênicas, agrotóxicos e na expulsão dos trabalhadores. “Agrotóxico não é necessidade agronômica, é para substituir a mão de obra, porque quanto menos trabalhador na fazenda, maior o lucro. Daí também a mecanização. Uma colheitadeira de algodão substitui 300 trabalhadores”, explica Stédile.
@@ -190,7 +190,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-      **** pais_br jornal_brasildefato * ano_2024 
+      **** *pais_br *jornal_brasildefato *ano_2024 
       Estamos assistindo há semanas (ou meses?) a mais espetacular estação de queimadas da história do país, ainda em curso e mais sinistra do que o Dia do Fogo de 2019 ou o mar de chamas de 2004. Já é um sinal preocupante para o meio ambiente do Brasil e, pela sua amplitude, do planeta, que tenhamos tal nome de batismo para o período de inverno. Mas a ocupação acelerada das fronteiras agrícolas pelo agronegócio, desde o tempo da ditadura militar, habituou-nos às imagens, cada vez mais gigantescas de florestas e outros ecossistemas sendo devorados pelas chamas ao longo de meses.
 Nos anos setenta, foi um escândalo internacional a queimada de uma propriedade de cem mil hectares no Pará, pertencente à empresa alemã Volkswagen. No Brasil, este fato não chegou a ser notícia, a não ser quando denunciado no exterior ao ser detectado por fotografias de satélite.
 De lá para cá, as queimadas viraram rotina e foram se expandindo, do arco de fogo subindo pelo mapa a partir do sul da Amazônia, do oeste do Mato Grosso ao leste do Pará, aos incêndios na intensa ocupação de Rondônia, Roraima e Acre e expandindo-se para o Cerrado e o Pantanal.
